--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484729_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484729_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>1.1458</v>
+        <v>1.0497</v>
       </c>
       <c r="E2" t="n">
-        <v>1.1711</v>
+        <v>1.366</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.0253</v>
+        <v>-0.3163</v>
       </c>
       <c r="G2" t="n">
         <v>-0.2289</v>
@@ -610,13 +610,13 @@
         <v>0.7548</v>
       </c>
       <c r="S2" t="n">
-        <v>0.2052</v>
+        <v>0.109</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.2787</v>
+        <v>-0.0838</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4839</v>
+        <v>0.1929</v>
       </c>
       <c r="V2" t="n">
         <v>1.547</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>K. FEDOROV</t>
+          <t>A. MANDU</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,58 +643,58 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.2375</v>
+        <v>-0.381</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8544</v>
+        <v>0.254</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.0919</v>
+        <v>-0.635</v>
       </c>
       <c r="G3" t="n">
-        <v>-1.7723</v>
+        <v>-0.3076</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.1487</v>
+        <v>-0.3076</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.6236</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.9767</v>
+        <v>0.3592</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.3271</v>
+        <v>0.3592</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.6496</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.7956</v>
+        <v>-0.6667999999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1784</v>
+        <v>-0.6667999999999999</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.9741</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>0.3774</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>0.3774</v>
       </c>
       <c r="S3" t="n">
-        <v>1.5349</v>
+        <v>-0.4509</v>
       </c>
       <c r="T3" t="n">
-        <v>1.8311</v>
+        <v>-0.1052</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2963</v>
+        <v>-0.3456</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. MANDU</t>
+          <t>G. ESQUEMBRE MORUGAN</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,40 +721,40 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.4075</v>
+        <v>-0.774</v>
       </c>
       <c r="E4" t="n">
-        <v>0.254</v>
+        <v>0.7232</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.6615</v>
+        <v>-1.4972</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.3076</v>
+        <v>-0.6329</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.3076</v>
+        <v>-1.6481</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1.0152</v>
       </c>
       <c r="J4" t="n">
-        <v>0.3592</v>
+        <v>0.6677</v>
       </c>
       <c r="K4" t="n">
-        <v>0.3592</v>
+        <v>0.0423</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>0.6254999999999999</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.6667999999999999</v>
+        <v>-1.3007</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.6667999999999999</v>
+        <v>-1.6904</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>0.3897</v>
       </c>
       <c r="P4" t="n">
         <v>0.3774</v>
@@ -766,28 +766,28 @@
         <v>0.3774</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.4773</v>
+        <v>-0.2166</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.1052</v>
+        <v>0.0555</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.3721</v>
+        <v>-0.2722</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>-0.3018</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-0.3018</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>G. ESQUEMBRE MORUGAN</t>
+          <t>K. FEDOROV</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.4733</v>
+        <v>-1.4151</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9181</v>
+        <v>-0.2174</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.3914</v>
+        <v>-1.1977</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.6329</v>
+        <v>-1.7723</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.6481</v>
+        <v>-0.1487</v>
       </c>
       <c r="I5" t="n">
-        <v>1.0152</v>
+        <v>-1.6236</v>
       </c>
       <c r="J5" t="n">
-        <v>0.6677</v>
+        <v>-0.9767</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0423</v>
+        <v>-0.3271</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6254999999999999</v>
+        <v>-0.6496</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.3007</v>
+        <v>-0.7956</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.6904</v>
+        <v>0.1784</v>
       </c>
       <c r="O5" t="n">
-        <v>0.3897</v>
+        <v>-0.9741</v>
       </c>
       <c r="P5" t="n">
-        <v>0.3774</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.3774</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.3573</v>
       </c>
       <c r="T5" t="n">
-        <v>0.2504</v>
+        <v>0.7593</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1663</v>
+        <v>-0.4021</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.3018</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.3018</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.8904</v>
+        <v>-2.2092</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.0929</v>
+        <v>-0.3852</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.7975</v>
+        <v>-1.8239</v>
       </c>
       <c r="G6" t="n">
         <v>-3.2892</v>
@@ -922,13 +922,13 @@
         <v>0.3774</v>
       </c>
       <c r="S6" t="n">
-        <v>0.07820000000000001</v>
+        <v>-0.2406</v>
       </c>
       <c r="T6" t="n">
-        <v>0.3585</v>
+        <v>0.06619999999999999</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2804</v>
+        <v>-0.3068</v>
       </c>
       <c r="V6" t="n">
         <v>1.8868</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. JAQUET</t>
+          <t>I. DE ANDREA LUNA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-3.7976</v>
+        <v>-3.5125</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.5461</v>
+        <v>-1.7282</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.2514</v>
+        <v>-1.7842</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.4569</v>
+        <v>-1.1337</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0368</v>
+        <v>-0.7184</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.4937</v>
+        <v>-0.4153</v>
       </c>
       <c r="J7" t="n">
-        <v>1.0463</v>
+        <v>1.4612</v>
       </c>
       <c r="K7" t="n">
-        <v>2.3454</v>
+        <v>1.3789</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.2991</v>
+        <v>0.0823</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.5032</v>
+        <v>-2.5949</v>
       </c>
       <c r="N7" t="n">
-        <v>-2.3086</v>
+        <v>-2.0973</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.1946</v>
+        <v>-0.4976</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.3209</v>
+        <v>-3.2079</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.0757</v>
+        <v>-3.9627</v>
       </c>
       <c r="R7" t="n">
         <v>0.7548</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.0387</v>
+        <v>-0.416</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.5168</v>
+        <v>-0.4719</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.522</v>
+        <v>0.0559</v>
       </c>
       <c r="V7" t="n">
-        <v>0.019</v>
+        <v>1.2452</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.2452</v>
       </c>
       <c r="X7" t="n">
-        <v>0.019</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>I. DE ANDREA LUNA</t>
+          <t>A. JAQUET</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.8048</v>
+        <v>-3.9034</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.0205</v>
+        <v>-1.5461</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.7842</v>
+        <v>-2.3573</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.1337</v>
+        <v>-1.4569</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.7184</v>
+        <v>0.0368</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4153</v>
+        <v>-1.4937</v>
       </c>
       <c r="J8" t="n">
-        <v>1.4612</v>
+        <v>1.0463</v>
       </c>
       <c r="K8" t="n">
-        <v>1.3789</v>
+        <v>2.3454</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0823</v>
+        <v>-1.2991</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.5949</v>
+        <v>-2.5032</v>
       </c>
       <c r="N8" t="n">
-        <v>-2.0973</v>
+        <v>-2.3086</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.4976</v>
+        <v>-0.1946</v>
       </c>
       <c r="P8" t="n">
-        <v>-3.2079</v>
+        <v>-1.3209</v>
       </c>
       <c r="Q8" t="n">
-        <v>-3.9627</v>
+        <v>-2.0757</v>
       </c>
       <c r="R8" t="n">
         <v>0.7548</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.7083</v>
+        <v>-1.1445</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.7642</v>
+        <v>-0.5168</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0559</v>
+        <v>-0.6278</v>
       </c>
       <c r="V8" t="n">
-        <v>1.2452</v>
+        <v>0.019</v>
       </c>
       <c r="W8" t="n">
-        <v>1.2452</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>0.019</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-5.091</v>
+        <v>-4.8878</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.9331</v>
+        <v>-1.8357</v>
       </c>
       <c r="F9" t="n">
-        <v>-3.1579</v>
+        <v>-3.0521</v>
       </c>
       <c r="G9" t="n">
         <v>-3.9163</v>
@@ -1156,13 +1156,13 @@
         <v>0.7548</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.4391</v>
+        <v>-1.2358</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.6343</v>
+        <v>-0.5369</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.8047</v>
+        <v>-0.6989</v>
       </c>
       <c r="V9" t="n">
         <v>-0.3018</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-7.1335</v>
+        <v>-6.0714</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.5945</v>
+        <v>-2.7176</v>
       </c>
       <c r="F10" t="n">
-        <v>-3.539</v>
+        <v>-3.3539</v>
       </c>
       <c r="G10" t="n">
         <v>-5.1707</v>
@@ -1234,13 +1234,13 @@
         <v>0.9435</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.6801</v>
+        <v>-0.618</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5044</v>
+        <v>0.3725</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.1757</v>
+        <v>-0.9905</v>
       </c>
       <c r="V10" t="n">
         <v>-1.2262</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-8.9702</v>
+        <v>-9.1219</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.2361</v>
+        <v>-3.6259</v>
       </c>
       <c r="F11" t="n">
-        <v>-5.7341</v>
+        <v>-5.496</v>
       </c>
       <c r="G11" t="n">
         <v>-6.4017</v>
@@ -1312,13 +1312,13 @@
         <v>1.1322</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.5685</v>
+        <v>-0.7201</v>
       </c>
       <c r="T11" t="n">
-        <v>0.68</v>
+        <v>0.2903</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.2485</v>
+        <v>-1.0104</v>
       </c>
       <c r="V11" t="n">
         <v>-1.2452</v>
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-9.422800000000001</v>
+        <v>-9.520200000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>-6.2861</v>
+        <v>-6.3835</v>
       </c>
       <c r="F12" t="n">
         <v>-3.1367</v>
@@ -1390,10 +1390,10 @@
         <v>0.7548</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.6837</v>
+        <v>-0.7811</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.1611</v>
+        <v>-0.2586</v>
       </c>
       <c r="U12" t="n">
         <v>-0.5225</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-12.6578</v>
+        <v>-11.9938</v>
       </c>
       <c r="E13" t="n">
-        <v>-6.1938</v>
+        <v>-5.6092</v>
       </c>
       <c r="F13" t="n">
-        <v>-6.464</v>
+        <v>-6.3846</v>
       </c>
       <c r="G13" t="n">
         <v>-4.5761</v>
@@ -1468,13 +1468,13 @@
         <v>0.5661</v>
       </c>
       <c r="S13" t="n">
-        <v>-2.0816</v>
+        <v>-1.4176</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.4109</v>
+        <v>-0.8263</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.6707</v>
+        <v>-0.5913</v>
       </c>
       <c r="V13" t="n">
         <v>-2.7922</v>
@@ -1501,10 +1501,10 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-52.74060000000001</v>
+        <v>-52.7406</v>
       </c>
       <c r="E14" t="n">
-        <v>-21.7055</v>
+        <v>-21.7056</v>
       </c>
       <c r="F14" t="n">
         <v>-31.0349</v>
@@ -1516,7 +1516,7 @@
         <v>-25.7551</v>
       </c>
       <c r="I14" t="n">
-        <v>-8.9833</v>
+        <v>-8.983300000000002</v>
       </c>
       <c r="J14" t="n">
         <v>-6.8628</v>
@@ -1546,16 +1546,16 @@
         <v>7.548</v>
       </c>
       <c r="S14" t="n">
-        <v>-6.774999999999999</v>
+        <v>-6.774900000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.2556</v>
+        <v>-1.2557</v>
       </c>
       <c r="U14" t="n">
-        <v>-5.5194</v>
+        <v>-5.5193</v>
       </c>
       <c r="V14" t="n">
-        <v>-1.791800000000001</v>
+        <v>-1.7918</v>
       </c>
       <c r="W14" t="n">
         <v>3.3958</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>9.805</v>
+        <v>9.338200000000001</v>
       </c>
       <c r="E15" t="n">
-        <v>7.5868</v>
+        <v>6.8073</v>
       </c>
       <c r="F15" t="n">
-        <v>2.2182</v>
+        <v>2.5309</v>
       </c>
       <c r="G15" t="n">
         <v>7.097</v>
@@ -1624,13 +1624,13 @@
         <v>1.887</v>
       </c>
       <c r="S15" t="n">
-        <v>1.1798</v>
+        <v>0.7131</v>
       </c>
       <c r="T15" t="n">
-        <v>1.302</v>
+        <v>0.5225</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1222</v>
+        <v>0.1905</v>
       </c>
       <c r="V15" t="n">
         <v>0.5846</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. BEDIA FERRER</t>
+          <t>J. MERENCIO MORENO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,58 +1657,58 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>8.8085</v>
+        <v>7.8328</v>
       </c>
       <c r="E16" t="n">
-        <v>6.1876</v>
+        <v>4.0024</v>
       </c>
       <c r="F16" t="n">
-        <v>2.6208</v>
+        <v>3.8304</v>
       </c>
       <c r="G16" t="n">
-        <v>6.1267</v>
+        <v>5.358</v>
       </c>
       <c r="H16" t="n">
-        <v>5.9446</v>
+        <v>2.7282</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1821</v>
+        <v>2.6298</v>
       </c>
       <c r="J16" t="n">
-        <v>5.6404</v>
+        <v>3.8108</v>
       </c>
       <c r="K16" t="n">
-        <v>5.3936</v>
+        <v>1.2678</v>
       </c>
       <c r="L16" t="n">
-        <v>0.2468</v>
+        <v>2.543</v>
       </c>
       <c r="M16" t="n">
-        <v>0.4863</v>
+        <v>1.5471</v>
       </c>
       <c r="N16" t="n">
-        <v>0.551</v>
+        <v>1.4604</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.06469999999999999</v>
+        <v>0.0868</v>
       </c>
       <c r="P16" t="n">
-        <v>0.5661</v>
+        <v>1.887</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.9435</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.5096</v>
+        <v>1.887</v>
       </c>
       <c r="S16" t="n">
-        <v>2.1157</v>
+        <v>0.5879</v>
       </c>
       <c r="T16" t="n">
-        <v>1.4907</v>
+        <v>0.1916</v>
       </c>
       <c r="U16" t="n">
-        <v>0.625</v>
+        <v>0.3963</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. MERENCIO MORENO</t>
+          <t>J. BEDIA FERRER</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,58 +1735,58 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>6.7935</v>
+        <v>7.7825</v>
       </c>
       <c r="E17" t="n">
-        <v>3.2229</v>
+        <v>5.5056</v>
       </c>
       <c r="F17" t="n">
-        <v>3.5706</v>
+        <v>2.2769</v>
       </c>
       <c r="G17" t="n">
-        <v>5.358</v>
+        <v>6.1267</v>
       </c>
       <c r="H17" t="n">
-        <v>2.7282</v>
+        <v>5.9446</v>
       </c>
       <c r="I17" t="n">
-        <v>2.6298</v>
+        <v>0.1821</v>
       </c>
       <c r="J17" t="n">
-        <v>3.8108</v>
+        <v>5.6404</v>
       </c>
       <c r="K17" t="n">
-        <v>1.2678</v>
+        <v>5.3936</v>
       </c>
       <c r="L17" t="n">
-        <v>2.543</v>
+        <v>0.2468</v>
       </c>
       <c r="M17" t="n">
-        <v>1.5471</v>
+        <v>0.4863</v>
       </c>
       <c r="N17" t="n">
-        <v>1.4604</v>
+        <v>0.551</v>
       </c>
       <c r="O17" t="n">
-        <v>0.0868</v>
+        <v>-0.06469999999999999</v>
       </c>
       <c r="P17" t="n">
-        <v>1.887</v>
+        <v>0.5661</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-0.9435</v>
       </c>
       <c r="R17" t="n">
-        <v>1.887</v>
+        <v>1.5096</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.4514</v>
+        <v>1.0897</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.5879</v>
+        <v>0.8087</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1365</v>
+        <v>0.2811</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>6.2427</v>
+        <v>5.5643</v>
       </c>
       <c r="E18" t="n">
-        <v>3.4026</v>
+        <v>2.6231</v>
       </c>
       <c r="F18" t="n">
-        <v>2.8401</v>
+        <v>2.9412</v>
       </c>
       <c r="G18" t="n">
         <v>3.6306</v>
@@ -1858,13 +1858,13 @@
         <v>1.5096</v>
       </c>
       <c r="S18" t="n">
-        <v>1.7442</v>
+        <v>1.0658</v>
       </c>
       <c r="T18" t="n">
-        <v>1.4196</v>
+        <v>0.6401</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3246</v>
+        <v>0.4257</v>
       </c>
       <c r="V18" t="n">
         <v>0.3018</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>4.108</v>
+        <v>4.7562</v>
       </c>
       <c r="E19" t="n">
-        <v>1.2297</v>
+        <v>1.3272</v>
       </c>
       <c r="F19" t="n">
-        <v>2.8782</v>
+        <v>3.429</v>
       </c>
       <c r="G19" t="n">
         <v>0.0192</v>
@@ -1936,13 +1936,13 @@
         <v>2.2644</v>
       </c>
       <c r="S19" t="n">
-        <v>0.2775</v>
+        <v>0.9257</v>
       </c>
       <c r="T19" t="n">
-        <v>0.5349</v>
+        <v>0.6323</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2574</v>
+        <v>0.2934</v>
       </c>
       <c r="V19" t="n">
         <v>2.4904</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>4.0322</v>
+        <v>4.6181</v>
       </c>
       <c r="E20" t="n">
-        <v>2.4067</v>
+        <v>3.2836</v>
       </c>
       <c r="F20" t="n">
-        <v>1.6255</v>
+        <v>1.3345</v>
       </c>
       <c r="G20" t="n">
         <v>4.7777</v>
@@ -2014,13 +2014,13 @@
         <v>1.887</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.104</v>
+        <v>0.4819</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.6343</v>
+        <v>0.2426</v>
       </c>
       <c r="U20" t="n">
-        <v>0.5303</v>
+        <v>0.2393</v>
       </c>
       <c r="V20" t="n">
         <v>-1.585</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. VALERO CHICA</t>
+          <t>F. GOMEZ CARBONELL</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>3.8736</v>
+        <v>3.6845</v>
       </c>
       <c r="E21" t="n">
-        <v>3.9581</v>
+        <v>1.7399</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.08450000000000001</v>
+        <v>1.9446</v>
       </c>
       <c r="G21" t="n">
-        <v>2.1165</v>
+        <v>2.2567</v>
       </c>
       <c r="H21" t="n">
-        <v>1.6857</v>
+        <v>2.0621</v>
       </c>
       <c r="I21" t="n">
-        <v>0.4309</v>
+        <v>0.1946</v>
       </c>
       <c r="J21" t="n">
-        <v>2.0798</v>
+        <v>2.0416</v>
       </c>
       <c r="K21" t="n">
-        <v>1.8657</v>
+        <v>2.5833</v>
       </c>
       <c r="L21" t="n">
-        <v>0.2142</v>
+        <v>-0.5417</v>
       </c>
       <c r="M21" t="n">
-        <v>0.0367</v>
+        <v>0.2152</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.18</v>
+        <v>-0.5212</v>
       </c>
       <c r="O21" t="n">
-        <v>0.2167</v>
+        <v>0.7363</v>
       </c>
       <c r="P21" t="n">
-        <v>1.3209</v>
+        <v>1.1322</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-0.9435</v>
       </c>
       <c r="R21" t="n">
-        <v>1.3209</v>
+        <v>2.0757</v>
       </c>
       <c r="S21" t="n">
-        <v>2.0022</v>
+        <v>0.6163999999999999</v>
       </c>
       <c r="T21" t="n">
-        <v>2.1991</v>
+        <v>0.34</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1969</v>
+        <v>0.2763</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.566</v>
+        <v>-0.3208</v>
       </c>
       <c r="W21" t="n">
-        <v>-0.3208</v>
+        <v>0.3018</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.2452</v>
+        <v>-0.6226</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>2.9199</v>
+        <v>3.5778</v>
       </c>
       <c r="E22" t="n">
-        <v>0.4823</v>
+        <v>0.7746</v>
       </c>
       <c r="F22" t="n">
-        <v>2.4376</v>
+        <v>2.8032</v>
       </c>
       <c r="G22" t="n">
         <v>-0.023</v>
@@ -2170,13 +2170,13 @@
         <v>1.5096</v>
       </c>
       <c r="S22" t="n">
-        <v>0.1881</v>
+        <v>0.8461</v>
       </c>
       <c r="T22" t="n">
-        <v>0.1793</v>
+        <v>0.4716</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0089</v>
+        <v>0.3745</v>
       </c>
       <c r="V22" t="n">
         <v>1.2452</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>F. GOMEZ CARBONELL</t>
+          <t>J. VALERO CHICA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>2.6837</v>
+        <v>3.1374</v>
       </c>
       <c r="E23" t="n">
-        <v>0.7655999999999999</v>
+        <v>2.9838</v>
       </c>
       <c r="F23" t="n">
-        <v>1.9181</v>
+        <v>0.1536</v>
       </c>
       <c r="G23" t="n">
-        <v>2.2567</v>
+        <v>2.1165</v>
       </c>
       <c r="H23" t="n">
-        <v>2.0621</v>
+        <v>1.6857</v>
       </c>
       <c r="I23" t="n">
-        <v>0.1946</v>
+        <v>0.4309</v>
       </c>
       <c r="J23" t="n">
-        <v>2.0416</v>
+        <v>2.0798</v>
       </c>
       <c r="K23" t="n">
-        <v>2.5833</v>
+        <v>1.8657</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.5417</v>
+        <v>0.2142</v>
       </c>
       <c r="M23" t="n">
-        <v>0.2152</v>
+        <v>0.0367</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.5212</v>
+        <v>-0.18</v>
       </c>
       <c r="O23" t="n">
-        <v>0.7363</v>
+        <v>0.2167</v>
       </c>
       <c r="P23" t="n">
-        <v>1.1322</v>
+        <v>1.3209</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.9435</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>2.0757</v>
+        <v>1.3209</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.3844</v>
+        <v>1.2659</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.6343</v>
+        <v>1.2247</v>
       </c>
       <c r="U23" t="n">
-        <v>0.2499</v>
+        <v>0.0412</v>
       </c>
       <c r="V23" t="n">
+        <v>-1.566</v>
+      </c>
+      <c r="W23" t="n">
         <v>-0.3208</v>
       </c>
-      <c r="W23" t="n">
-        <v>0.3018</v>
-      </c>
       <c r="X23" t="n">
-        <v>-0.6226</v>
+        <v>-1.2452</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>2.5396</v>
+        <v>2.8138</v>
       </c>
       <c r="E24" t="n">
-        <v>0.8587</v>
+        <v>1.0536</v>
       </c>
       <c r="F24" t="n">
-        <v>1.6808</v>
+        <v>1.7602</v>
       </c>
       <c r="G24" t="n">
         <v>2.4453</v>
@@ -2326,13 +2326,13 @@
         <v>1.1322</v>
       </c>
       <c r="S24" t="n">
-        <v>0.2075</v>
+        <v>0.4817</v>
       </c>
       <c r="T24" t="n">
-        <v>0.2504</v>
+        <v>0.4453</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.0429</v>
+        <v>0.0365</v>
       </c>
       <c r="V24" t="n">
         <v>0.6415999999999999</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>52.7407</v>
+        <v>54.0396</v>
       </c>
       <c r="E27" t="n">
-        <v>31.035</v>
+        <v>31.0351</v>
       </c>
       <c r="F27" t="n">
-        <v>21.7054</v>
+        <v>23.0045</v>
       </c>
       <c r="G27" t="n">
         <v>34.73869999999999</v>
@@ -2539,19 +2539,19 @@
         <v>22.3586</v>
       </c>
       <c r="L27" t="n">
-        <v>5.5174</v>
+        <v>5.517399999999999</v>
       </c>
       <c r="M27" t="n">
-        <v>6.8627</v>
+        <v>6.862699999999999</v>
       </c>
       <c r="N27" t="n">
-        <v>3.396699999999999</v>
+        <v>3.3967</v>
       </c>
       <c r="O27" t="n">
-        <v>3.465999999999999</v>
+        <v>3.466</v>
       </c>
       <c r="P27" t="n">
-        <v>9.435000000000002</v>
+        <v>9.435</v>
       </c>
       <c r="Q27" t="n">
         <v>-7.548</v>
@@ -2560,22 +2560,22 @@
         <v>16.983</v>
       </c>
       <c r="S27" t="n">
-        <v>6.775199999999999</v>
+        <v>8.074200000000001</v>
       </c>
       <c r="T27" t="n">
-        <v>5.5195</v>
+        <v>5.519399999999999</v>
       </c>
       <c r="U27" t="n">
-        <v>1.2558</v>
+        <v>2.5548</v>
       </c>
       <c r="V27" t="n">
-        <v>1.7918</v>
+        <v>1.791800000000001</v>
       </c>
       <c r="W27" t="n">
-        <v>5.187600000000001</v>
+        <v>5.1876</v>
       </c>
       <c r="X27" t="n">
-        <v>-3.395800000000001</v>
+        <v>-3.3958</v>
       </c>
     </row>
   </sheetData>
